--- a/public/Plantilla Masiva.xlsx
+++ b/public/Plantilla Masiva.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpalacios\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://estudiodemoda-my.sharepoint.com/personal/aprendizti2_estudiodemoda_com_co/Documents/Documentos/Inventario TI/TI-HelpDesk/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525B3902-FAAD-46B7-AF16-04EBFFAEFA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -3848,28 +3848,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="9" max="9" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.42578125" customWidth="1"/>
-    <col min="16" max="16" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.44140625" customWidth="1"/>
+    <col min="16" max="16" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>25</v>
       </c>
@@ -3969,67 +3969,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DCFB67C-0DAD-444B-939C-CFF08ADEA543}">
   <dimension ref="A2:BT109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" customWidth="1"/>
     <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="42" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="24.42578125" customWidth="1"/>
-    <col min="18" max="18" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="24.44140625" customWidth="1"/>
+    <col min="18" max="18" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="24.44140625" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="24.42578125" customWidth="1"/>
-    <col min="25" max="25" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="24.42578125" customWidth="1"/>
-    <col min="30" max="31" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="24.42578125" customWidth="1"/>
-    <col min="34" max="34" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="24.42578125" customWidth="1"/>
-    <col min="36" max="37" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="24.42578125" customWidth="1"/>
-    <col min="39" max="40" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="24.42578125" customWidth="1"/>
-    <col min="42" max="42" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="43" max="45" width="24.42578125" customWidth="1"/>
-    <col min="46" max="46" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="24.42578125" customWidth="1"/>
-    <col min="49" max="49" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.44140625" customWidth="1"/>
+    <col min="25" max="25" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="24.44140625" customWidth="1"/>
+    <col min="30" max="31" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="24.44140625" customWidth="1"/>
+    <col min="34" max="34" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24.44140625" customWidth="1"/>
+    <col min="36" max="37" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24.44140625" customWidth="1"/>
+    <col min="39" max="40" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="24.44140625" customWidth="1"/>
+    <col min="42" max="42" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="45" width="24.44140625" customWidth="1"/>
+    <col min="46" max="46" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="24.44140625" customWidth="1"/>
+    <col min="49" max="49" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="34.44140625" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="32" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="53.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18.42578125" customWidth="1"/>
-    <col min="59" max="59" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="51.28515625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="68" max="69" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="27.28515625" customWidth="1"/>
+    <col min="52" max="52" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="53.109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="18.44140625" customWidth="1"/>
+    <col min="59" max="59" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="69" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -4288,7 +4288,7 @@
       <c r="AN14" s="4"/>
       <c r="AO14" s="3"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="AN15" s="13"/>
       <c r="AO15" s="5"/>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -4326,7 +4326,7 @@
       <c r="AN16" s="4"/>
       <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
         <v>49</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E20" t="s">
         <v>50</v>
       </c>
@@ -4364,147 +4364,147 @@
         <v>447</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E21" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E27" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E29" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E30" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E31" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E32" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E35" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E36" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E37" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E38" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E40" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E41" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E42" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E43" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E44" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E46" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E47" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E48" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>435</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="56" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>98</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="57" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>99</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="58" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>48</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="59" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>49</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>51</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>53</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="62" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>100</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="63" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>101</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="64" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>102</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>103</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>56</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="67" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>104</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="68" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>61</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="69" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>62</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="70" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>105</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="71" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>106</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="72" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>107</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="73" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>66</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="74" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>67</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="75" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>68</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="76" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>24</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="77" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>69</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="78" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>73</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="79" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>75</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="80" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>108</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="81" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>77</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI82" t="s">
         <v>327</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="83" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI83" t="s">
         <v>328</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="84" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI84" t="s">
         <v>329</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="85" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI85" t="s">
         <v>330</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="86" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI86" t="s">
         <v>331</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI87" t="s">
         <v>332</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="88" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI88" t="s">
         <v>333</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="89" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI89" t="s">
         <v>334</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="90" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI90" t="s">
         <v>335</v>
       </c>
@@ -6414,97 +6414,97 @@
         <v>386</v>
       </c>
     </row>
-    <row r="91" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI91" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="92" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI92" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="93" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI93" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="94" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI94" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="95" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI95" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="96" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:63" x14ac:dyDescent="0.3">
       <c r="BI96" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="97" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="97" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI97" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="98" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="98" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI98" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="99" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="99" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI99" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="100" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="100" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI100" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="101" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI101" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="102" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="102" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI102" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="103" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="103" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI103" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="104" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="104" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI104" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="105" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="105" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI105" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="106" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="106" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI106" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="107" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI107" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="108" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="108" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI108" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="109" spans="61:61" x14ac:dyDescent="0.25">
+    <row r="109" spans="61:61" x14ac:dyDescent="0.3">
       <c r="BI109" t="s">
         <v>351</v>
       </c>
@@ -6721,18 +6721,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6752,18 +6752,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3855E20C-B2B0-4925-850D-1C34AFA28120}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D5C9593-581C-4307-B105-BB177D71AAE3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3855E20C-B2B0-4925-850D-1C34AFA28120}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>